--- a/03_Outputs/all/idx1_servicio_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx1_servicio_loadings_y_tops.xlsx
@@ -396,7 +396,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.7109590908335826</v>
+        <v>0.7109590908335829</v>
       </c>
       <c r="D2">
         <v>0.4431740632553642</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.6652270547139657</v>
+        <v>0.6652270547139658</v>
       </c>
       <c r="D3">
-        <v>0.4146671455868541</v>
+        <v>0.414667145586854</v>
       </c>
       <c r="E3">
         <v>41.5</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.2280573104236471</v>
+        <v>0.2280573104236474</v>
       </c>
       <c r="D4">
-        <v>0.1421587911577817</v>
+        <v>0.1421587911577818</v>
       </c>
       <c r="E4">
         <v>14.2</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.02687625131415387</v>
+        <v>0.02687625131415342</v>
       </c>
       <c r="D5">
-        <v>0.020467901214393</v>
+        <v>0.02046790121439266</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.3497642938237708</v>
+        <v>-0.3497642938237709</v>
       </c>
       <c r="D6">
-        <v>0.2663667983539336</v>
+        <v>0.2663667983539337</v>
       </c>
       <c r="E6">
         <v>26.6</v>
@@ -504,7 +504,7 @@
         <v>0.9364521375282655</v>
       </c>
       <c r="D7">
-        <v>0.7131653004316734</v>
+        <v>0.7131653004316737</v>
       </c>
       <c r="E7">
         <v>71.3</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.7027196014602012</v>
+        <v>0.7027196014602008</v>
       </c>
       <c r="D8">
-        <v>0.4314031235857315</v>
+        <v>0.4314031235857313</v>
       </c>
       <c r="E8">
         <v>43.1</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.6596498347172848</v>
+        <v>-0.6596498347172852</v>
       </c>
       <c r="D9">
-        <v>0.4049623755741573</v>
+        <v>0.4049623755741576</v>
       </c>
       <c r="E9">
         <v>40.5</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.2665469138464652</v>
+        <v>-0.266546913846465</v>
       </c>
       <c r="D10">
-        <v>0.1636345008401112</v>
+        <v>0.1636345008401111</v>
       </c>
       <c r="E10">
         <v>16.4</v>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.6120261908401192</v>
+        <v>0.6120261908401188</v>
       </c>
     </row>
     <row r="3">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3399167061053555</v>
+        <v>0.339916706105356</v>
       </c>
     </row>
     <row r="4">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.0480571030545253</v>
+        <v>0.04805710305452526</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.7109590908335826</v>
+        <v>0.7109590908335829</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6652270547139657</v>
+        <v>0.6652270547139658</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.2280573104236471</v>
+        <v>0.2280573104236474</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.3497642938237708</v>
+        <v>-0.3497642938237709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.02687625131415387</v>
+        <v>0.02687625131415342</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
